--- a/income_details.xlsx
+++ b/income_details.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,13 +413,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Trading</v>
+        <v>income</v>
       </c>
       <c r="B2">
         <v>100000</v>
       </c>
       <c r="C2" s="1">
-        <v>45960.20847222222</v>
+        <v>45968.20847222222</v>
       </c>
     </row>
     <row r="3">
@@ -435,10 +435,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>House Rent</v>
+        <v>shop Rent</v>
       </c>
       <c r="B4">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="C4" s="1">
         <v>45959.20847222222</v>
@@ -446,29 +446,18 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>shop Rent</v>
+        <v>watch</v>
       </c>
       <c r="B5">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="C5" s="1">
-        <v>45959.20847222222</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>watch</v>
-      </c>
-      <c r="B6">
-        <v>1000</v>
-      </c>
-      <c r="C6" s="1">
         <v>45726.20847222222</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/income_details.xlsx
+++ b/income_details.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -424,40 +424,150 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Salary</v>
+        <v>November Salary</v>
       </c>
       <c r="B3">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="C3" s="1">
-        <v>45959.20847222222</v>
+        <v>45963.20847222222</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>shop Rent</v>
+        <v xml:space="preserve">December Salary </v>
       </c>
       <c r="B4">
-        <v>5000</v>
+        <v>25000</v>
       </c>
       <c r="C4" s="1">
-        <v>45959.20847222222</v>
+        <v>45963.20847222222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>January Salary</v>
+      </c>
+      <c r="B5">
+        <v>25000</v>
+      </c>
+      <c r="C5" s="1">
+        <v>45963.20847222222</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Park Rent</v>
+      </c>
+      <c r="B6">
+        <v>50000</v>
+      </c>
+      <c r="C6" s="1">
+        <v>45962.20847222222</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Glass Miror</v>
+      </c>
+      <c r="B7">
+        <v>150000</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45962.20847222222</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Bike Sale</v>
+      </c>
+      <c r="B8">
+        <v>80000</v>
+      </c>
+      <c r="C8" s="1">
+        <v>45962.20847222222</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v xml:space="preserve">Car Sale </v>
+      </c>
+      <c r="B9">
+        <v>500000</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45962.20847222222</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>new salary</v>
+      </c>
+      <c r="B10">
+        <v>12000</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45962.20847222222</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>old income</v>
+      </c>
+      <c r="B11">
+        <v>533</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45962.20847222222</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>apple</v>
+      </c>
+      <c r="B12">
+        <v>232</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45962.20847222222</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="B13">
+        <v>30000</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45959.20847222222</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>shop Rent</v>
+      </c>
+      <c r="B14">
+        <v>5000</v>
+      </c>
+      <c r="C14" s="1">
+        <v>45959.20847222222</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
         <v>watch</v>
       </c>
-      <c r="B5">
+      <c r="B15">
         <v>1000</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C15" s="1">
         <v>45726.20847222222</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>